--- a/output-submit/渠道资源再配置建议.xlsx
+++ b/output-submit/渠道资源再配置建议.xlsx
@@ -888,13 +888,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="C2:C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"自营,平台,即时零售"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"增投,维持,收缩"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="P2:P200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"已确认,待补"</formula1>
     </dataValidation>
   </dataValidations>
